--- a/results/ai_run/682_z29/5_quantification/682_z29_quantification.xlsx
+++ b/results/ai_run/682_z29/5_quantification/682_z29_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>12.6154</v>
+        <v>8.2308</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>4.5376</v>
+        <v>3.4194</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.1329</v>
+        <v>4.4574</v>
       </c>
       <c r="D25" t="n">
-        <v>6.4136</v>
+        <v>4.6693</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0161</v>
+        <v>1.0284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -2269,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
@@ -2592,7 +2592,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>192</v>
@@ -2631,7 +2631,7 @@
         <v>0.02597872</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.6708</v>
+        <v>1.5262</v>
       </c>
       <c r="Z2" t="n">
         <v>85</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M4" t="n">
         <v>363</v>
@@ -2842,7 +2842,7 @@
         <v>0.05259338</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.6219</v>
+        <v>4.9664</v>
       </c>
       <c r="Z4" t="n">
         <v>319</v>
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
         <v>459</v>
@@ -2949,7 +2949,7 @@
         <v>0.04528952</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.1733</v>
+        <v>3.5567</v>
       </c>
       <c r="Z5" t="n">
         <v>428</v>
@@ -3017,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
         <v>460</v>
@@ -3056,7 +3056,7 @@
         <v>0.04550439</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.502000000000001</v>
+        <v>4.6761</v>
       </c>
       <c r="Z6" t="n">
         <v>432</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="M7" t="n">
         <v>481</v>
@@ -3163,7 +3163,7 @@
         <v>0.04813295</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.9377</v>
+        <v>4.6693</v>
       </c>
       <c r="Z7" t="n">
         <v>429</v>
@@ -3231,7 +3231,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M8" t="n">
         <v>392</v>
@@ -3270,7 +3270,7 @@
         <v>0.0383896</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.0268</v>
+        <v>3.4073</v>
       </c>
       <c r="Z8" t="n">
         <v>379</v>
@@ -3338,7 +3338,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
         <v>376</v>
@@ -3377,7 +3377,7 @@
         <v>0.04314491</v>
       </c>
       <c r="Y9" t="n">
-        <v>6.9723</v>
+        <v>3.4861</v>
       </c>
       <c r="Z9" t="n">
         <v>358</v>
@@ -3445,7 +3445,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="M10" t="n">
         <v>222</v>
@@ -3484,7 +3484,7 @@
         <v>0.03463894</v>
       </c>
       <c r="Y10" t="n">
-        <v>8.925599999999999</v>
+        <v>5.7379</v>
       </c>
       <c r="Z10" t="n">
         <v>199</v>
@@ -3659,7 +3659,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
         <v>191</v>
@@ -3698,7 +3698,7 @@
         <v>0.03588517</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5618</v>
+        <v>3.0899</v>
       </c>
       <c r="Z12" t="n">
         <v>191</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
         <v>210</v>
@@ -3805,7 +3805,7 @@
         <v>0.03326489</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.1143</v>
+        <v>2.7175</v>
       </c>
       <c r="Z13" t="n">
         <v>157</v>
@@ -3873,7 +3873,7 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="M14" t="n">
         <v>445</v>
@@ -3912,7 +3912,7 @@
         <v>0.03963827</v>
       </c>
       <c r="Y14" t="n">
-        <v>6.2821</v>
+        <v>4.3189</v>
       </c>
       <c r="Z14" t="n">
         <v>388</v>
@@ -3980,7 +3980,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
         <v>272</v>
@@ -4019,7 +4019,7 @@
         <v>0.0276098</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.4136</v>
+        <v>4.9336</v>
       </c>
       <c r="Z15" t="n">
         <v>253</v>
@@ -4066,7 +4066,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
         <v>245</v>
@@ -4105,7 +4105,7 @@
         <v>0.05268046</v>
       </c>
       <c r="Y16" t="n">
-        <v>12.6433</v>
+        <v>4.2144</v>
       </c>
       <c r="Z16" t="n">
         <v>177</v>
